--- a/artfynd/A 52616-2021 artfynd.xlsx
+++ b/artfynd/A 52616-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52616-2021 artfynd.xlsx
+++ b/artfynd/A 52616-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>110940616</v>
       </c>
       <c r="B2" t="n">
-        <v>93248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683573.9792590602</v>
+        <v>683573</v>
       </c>
       <c r="R2" t="n">
-        <v>6559924.534570459</v>
+        <v>6559925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -824,12 +819,7 @@
         <v>110940619</v>
       </c>
       <c r="B3" t="n">
-        <v>93248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -875,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683529.8509523764</v>
+        <v>683529</v>
       </c>
       <c r="R3" t="n">
-        <v>6559932.175508781</v>
+        <v>6559932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -947,15 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110940624</v>
+        <v>110940620</v>
       </c>
       <c r="B4" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,27 +948,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,10 +977,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683518.7684673058</v>
+        <v>683529</v>
       </c>
       <c r="R4" t="n">
-        <v>6559937.809296284</v>
+        <v>6559932</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1037,7 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,21 +1033,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1082,12 +1052,7 @@
         <v>110940623</v>
       </c>
       <c r="B5" t="n">
-        <v>93171</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683527.5990270684</v>
+        <v>683528</v>
       </c>
       <c r="R5" t="n">
-        <v>6559936.178501653</v>
+        <v>6559936</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1199,12 +1164,7 @@
         <v>110940632</v>
       </c>
       <c r="B6" t="n">
-        <v>93171</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683512.615208055</v>
+        <v>683513</v>
       </c>
       <c r="R6" t="n">
-        <v>6559851.688061324</v>
+        <v>6559852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,15 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110940615</v>
+        <v>110940629</v>
       </c>
       <c r="B7" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,16 +1279,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>105076</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1341,24 +1296,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjursta, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683644.248538044</v>
+        <v>683514</v>
       </c>
       <c r="R7" t="n">
-        <v>6559876.524672879</v>
+        <v>6559926</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1390,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1400,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,23 +1381,27 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Satt på grov nedfallen aspgren.</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula # Satt på grov nedfallen aspgren.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,22 +1412,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110940620</v>
+        <v>110940615</v>
       </c>
       <c r="B8" t="n">
-        <v>93171</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,39 +1430,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjursta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683529.8509523764</v>
+        <v>683644</v>
       </c>
       <c r="R8" t="n">
-        <v>6559932.175508781</v>
+        <v>6559877</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,7 +1496,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1533,7 +1506,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,8 +1515,24 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1553,22 +1542,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110940629</v>
+        <v>110940624</v>
       </c>
       <c r="B9" t="n">
-        <v>9310</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,46 +1560,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105076</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1624,10 +1589,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683513.6858004527</v>
+        <v>683518</v>
       </c>
       <c r="R9" t="n">
-        <v>6559925.744634388</v>
+        <v>6559938</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,7 +1624,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1669,7 +1634,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,22 +1648,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Satt på grov nedfallen aspgren.</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Populus tremula # Satt på grov nedfallen aspgren.</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1719,12 +1679,7 @@
         <v>111153905</v>
       </c>
       <c r="B10" t="n">
-        <v>57580</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1765,10 +1720,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683503.9019435373</v>
+        <v>683504</v>
       </c>
       <c r="R10" t="n">
-        <v>6559925.787848474</v>
+        <v>6559926</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1798,19 +1753,9 @@
           <t>2023-07-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-07-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 52616-2021 artfynd.xlsx
+++ b/artfynd/A 52616-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -813,6 +818,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940616</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940619</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1046,6 +1061,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1158,6 +1178,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940623</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940632</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1416,6 +1446,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940629</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1546,6 +1581,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1673,6 +1713,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110940624</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1780,8 +1825,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111153905</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>